--- a/Code/Jupiter/Connect4/Logs/PPO/PPO-2000-PPO-L-True-SP_FINALE-PPO_842 - at-2026-04-22 17-09-40-benchmark.xlsx
+++ b/Code/Jupiter/Connect4/Logs/PPO/PPO-2000-PPO-L-True-SP_FINALE-PPO_842 - at-2026-04-22 17-09-40-benchmark.xlsx
@@ -431,7 +431,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T22"/>
+  <dimension ref="A1:T72"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:20">
@@ -1735,6 +1735,2956 @@
         <v>1</v>
       </c>
     </row>
+    <row r="23" spans="1:20">
+      <c r="A23">
+        <v>420</v>
+      </c>
+      <c r="B23">
+        <v>0.000194</v>
+      </c>
+      <c r="C23">
+        <v>0.02</v>
+      </c>
+      <c r="D23">
+        <v>0.485</v>
+      </c>
+      <c r="E23">
+        <v>0.5763356423820739</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+      <c r="H23">
+        <v>0.995</v>
+      </c>
+      <c r="I23">
+        <v>1</v>
+      </c>
+      <c r="J23">
+        <v>1</v>
+      </c>
+      <c r="K23">
+        <v>0.5</v>
+      </c>
+      <c r="L23">
+        <v>0.5</v>
+      </c>
+      <c r="M23">
+        <v>0.5</v>
+      </c>
+      <c r="N23">
+        <v>0.5</v>
+      </c>
+      <c r="O23">
+        <v>0.5</v>
+      </c>
+      <c r="P23">
+        <v>1</v>
+      </c>
+      <c r="Q23">
+        <v>0.5</v>
+      </c>
+      <c r="R23">
+        <v>0.5</v>
+      </c>
+      <c r="S23">
+        <v>1</v>
+      </c>
+      <c r="T23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20">
+      <c r="A24">
+        <v>440</v>
+      </c>
+      <c r="B24">
+        <v>0.24125</v>
+      </c>
+      <c r="C24">
+        <v>0.5</v>
+      </c>
+      <c r="D24">
+        <v>0.965</v>
+      </c>
+      <c r="E24">
+        <v>0.9151191676558078</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+      <c r="H24">
+        <v>1</v>
+      </c>
+      <c r="I24">
+        <v>1</v>
+      </c>
+      <c r="J24">
+        <v>1</v>
+      </c>
+      <c r="K24">
+        <v>0.5</v>
+      </c>
+      <c r="L24">
+        <v>0.5</v>
+      </c>
+      <c r="M24">
+        <v>0.5</v>
+      </c>
+      <c r="N24">
+        <v>0.5</v>
+      </c>
+      <c r="O24">
+        <v>0.5</v>
+      </c>
+      <c r="P24">
+        <v>1</v>
+      </c>
+      <c r="Q24">
+        <v>1</v>
+      </c>
+      <c r="R24">
+        <v>1</v>
+      </c>
+      <c r="S24">
+        <v>1</v>
+      </c>
+      <c r="T24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20">
+      <c r="A25">
+        <v>460</v>
+      </c>
+      <c r="B25">
+        <v>0.24125</v>
+      </c>
+      <c r="C25">
+        <v>0.5</v>
+      </c>
+      <c r="D25">
+        <v>0.965</v>
+      </c>
+      <c r="E25">
+        <v>0.5763073814846001</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+      <c r="H25">
+        <v>0.99</v>
+      </c>
+      <c r="I25">
+        <v>1</v>
+      </c>
+      <c r="J25">
+        <v>1</v>
+      </c>
+      <c r="K25">
+        <v>0.5</v>
+      </c>
+      <c r="L25">
+        <v>0.5</v>
+      </c>
+      <c r="M25">
+        <v>0.5</v>
+      </c>
+      <c r="N25">
+        <v>0.5</v>
+      </c>
+      <c r="O25">
+        <v>0.5</v>
+      </c>
+      <c r="P25">
+        <v>1</v>
+      </c>
+      <c r="Q25">
+        <v>0.5</v>
+      </c>
+      <c r="R25">
+        <v>0.5</v>
+      </c>
+      <c r="S25">
+        <v>1</v>
+      </c>
+      <c r="T25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20">
+      <c r="A26">
+        <v>480</v>
+      </c>
+      <c r="B26">
+        <v>0.24125</v>
+      </c>
+      <c r="C26">
+        <v>0.5</v>
+      </c>
+      <c r="D26">
+        <v>0.965</v>
+      </c>
+      <c r="E26">
+        <v>0.9150343849633867</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+      <c r="H26">
+        <v>0.985</v>
+      </c>
+      <c r="I26">
+        <v>1</v>
+      </c>
+      <c r="J26">
+        <v>1</v>
+      </c>
+      <c r="K26">
+        <v>0.5</v>
+      </c>
+      <c r="L26">
+        <v>0.5</v>
+      </c>
+      <c r="M26">
+        <v>0.5</v>
+      </c>
+      <c r="N26">
+        <v>0.5</v>
+      </c>
+      <c r="O26">
+        <v>0.5</v>
+      </c>
+      <c r="P26">
+        <v>1</v>
+      </c>
+      <c r="Q26">
+        <v>1</v>
+      </c>
+      <c r="R26">
+        <v>1</v>
+      </c>
+      <c r="S26">
+        <v>1</v>
+      </c>
+      <c r="T26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20">
+      <c r="A27">
+        <v>500</v>
+      </c>
+      <c r="B27">
+        <v>0.24125</v>
+      </c>
+      <c r="C27">
+        <v>0.5</v>
+      </c>
+      <c r="D27">
+        <v>0.965</v>
+      </c>
+      <c r="E27">
+        <v>0.9150626458608604</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
+      <c r="H27">
+        <v>0.99</v>
+      </c>
+      <c r="I27">
+        <v>1</v>
+      </c>
+      <c r="J27">
+        <v>1</v>
+      </c>
+      <c r="K27">
+        <v>0.5</v>
+      </c>
+      <c r="L27">
+        <v>0.5</v>
+      </c>
+      <c r="M27">
+        <v>0.5</v>
+      </c>
+      <c r="N27">
+        <v>0.5</v>
+      </c>
+      <c r="O27">
+        <v>0.5</v>
+      </c>
+      <c r="P27">
+        <v>1</v>
+      </c>
+      <c r="Q27">
+        <v>1</v>
+      </c>
+      <c r="R27">
+        <v>1</v>
+      </c>
+      <c r="S27">
+        <v>1</v>
+      </c>
+      <c r="T27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20">
+      <c r="A28">
+        <v>520</v>
+      </c>
+      <c r="B28">
+        <v>0.241875</v>
+      </c>
+      <c r="C28">
+        <v>0.5</v>
+      </c>
+      <c r="D28">
+        <v>0.9675</v>
+      </c>
+      <c r="E28">
+        <v>0.4966665254037427</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
+      <c r="H28">
+        <v>0.995</v>
+      </c>
+      <c r="I28">
+        <v>1</v>
+      </c>
+      <c r="J28">
+        <v>1</v>
+      </c>
+      <c r="K28">
+        <v>0.5</v>
+      </c>
+      <c r="L28">
+        <v>0.5</v>
+      </c>
+      <c r="M28">
+        <v>0.5</v>
+      </c>
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="O28">
+        <v>0.5</v>
+      </c>
+      <c r="P28">
+        <v>0.5</v>
+      </c>
+      <c r="Q28">
+        <v>0.5</v>
+      </c>
+      <c r="R28">
+        <v>0.5</v>
+      </c>
+      <c r="S28">
+        <v>1</v>
+      </c>
+      <c r="T28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20">
+      <c r="A29">
+        <v>540</v>
+      </c>
+      <c r="B29">
+        <v>0.24125</v>
+      </c>
+      <c r="C29">
+        <v>0.5</v>
+      </c>
+      <c r="D29">
+        <v>0.965</v>
+      </c>
+      <c r="E29">
+        <v>0.496638264506269</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+      <c r="H29">
+        <v>0.99</v>
+      </c>
+      <c r="I29">
+        <v>1</v>
+      </c>
+      <c r="J29">
+        <v>1</v>
+      </c>
+      <c r="K29">
+        <v>0.5</v>
+      </c>
+      <c r="L29">
+        <v>0.5</v>
+      </c>
+      <c r="M29">
+        <v>0.5</v>
+      </c>
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="O29">
+        <v>0.5</v>
+      </c>
+      <c r="P29">
+        <v>0.5</v>
+      </c>
+      <c r="Q29">
+        <v>0.5</v>
+      </c>
+      <c r="R29">
+        <v>0.5</v>
+      </c>
+      <c r="S29">
+        <v>1</v>
+      </c>
+      <c r="T29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20">
+      <c r="A30">
+        <v>560</v>
+      </c>
+      <c r="B30">
+        <v>0.2425</v>
+      </c>
+      <c r="C30">
+        <v>0.5</v>
+      </c>
+      <c r="D30">
+        <v>0.97</v>
+      </c>
+      <c r="E30">
+        <v>0.5074949708797769</v>
+      </c>
+      <c r="G30">
+        <v>1</v>
+      </c>
+      <c r="H30">
+        <v>0.99</v>
+      </c>
+      <c r="I30">
+        <v>1</v>
+      </c>
+      <c r="J30">
+        <v>1</v>
+      </c>
+      <c r="K30">
+        <v>0.5</v>
+      </c>
+      <c r="L30">
+        <v>1</v>
+      </c>
+      <c r="M30">
+        <v>0.5</v>
+      </c>
+      <c r="N30">
+        <v>0</v>
+      </c>
+      <c r="O30">
+        <v>0.5</v>
+      </c>
+      <c r="P30">
+        <v>0.5</v>
+      </c>
+      <c r="Q30">
+        <v>0.5</v>
+      </c>
+      <c r="R30">
+        <v>0.5</v>
+      </c>
+      <c r="S30">
+        <v>1</v>
+      </c>
+      <c r="T30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20">
+      <c r="A31">
+        <v>580</v>
+      </c>
+      <c r="B31">
+        <v>0.2425</v>
+      </c>
+      <c r="C31">
+        <v>0.5</v>
+      </c>
+      <c r="D31">
+        <v>0.97</v>
+      </c>
+      <c r="E31">
+        <v>0.4966665254037427</v>
+      </c>
+      <c r="G31">
+        <v>1</v>
+      </c>
+      <c r="H31">
+        <v>0.995</v>
+      </c>
+      <c r="I31">
+        <v>1</v>
+      </c>
+      <c r="J31">
+        <v>1</v>
+      </c>
+      <c r="K31">
+        <v>0.5</v>
+      </c>
+      <c r="L31">
+        <v>0.5</v>
+      </c>
+      <c r="M31">
+        <v>0.5</v>
+      </c>
+      <c r="N31">
+        <v>0</v>
+      </c>
+      <c r="O31">
+        <v>0.5</v>
+      </c>
+      <c r="P31">
+        <v>0.5</v>
+      </c>
+      <c r="Q31">
+        <v>0.5</v>
+      </c>
+      <c r="R31">
+        <v>0.5</v>
+      </c>
+      <c r="S31">
+        <v>1</v>
+      </c>
+      <c r="T31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20">
+      <c r="A32">
+        <v>600</v>
+      </c>
+      <c r="B32">
+        <v>0.24125</v>
+      </c>
+      <c r="C32">
+        <v>0.5</v>
+      </c>
+      <c r="D32">
+        <v>0.965</v>
+      </c>
+      <c r="E32">
+        <v>0.6110826105793299</v>
+      </c>
+      <c r="G32">
+        <v>1</v>
+      </c>
+      <c r="H32">
+        <v>0.99</v>
+      </c>
+      <c r="I32">
+        <v>1</v>
+      </c>
+      <c r="J32">
+        <v>1</v>
+      </c>
+      <c r="K32">
+        <v>0.5</v>
+      </c>
+      <c r="L32">
+        <v>0.5</v>
+      </c>
+      <c r="M32">
+        <v>0.5</v>
+      </c>
+      <c r="N32">
+        <v>0</v>
+      </c>
+      <c r="O32">
+        <v>0.5</v>
+      </c>
+      <c r="P32">
+        <v>0.5</v>
+      </c>
+      <c r="Q32">
+        <v>1</v>
+      </c>
+      <c r="R32">
+        <v>0.5</v>
+      </c>
+      <c r="S32">
+        <v>1</v>
+      </c>
+      <c r="T32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20">
+      <c r="A33">
+        <v>620</v>
+      </c>
+      <c r="B33">
+        <v>0.24125</v>
+      </c>
+      <c r="C33">
+        <v>0.5</v>
+      </c>
+      <c r="D33">
+        <v>0.965</v>
+      </c>
+      <c r="E33">
+        <v>0.6110826105793299</v>
+      </c>
+      <c r="G33">
+        <v>1</v>
+      </c>
+      <c r="H33">
+        <v>0.99</v>
+      </c>
+      <c r="I33">
+        <v>1</v>
+      </c>
+      <c r="J33">
+        <v>1</v>
+      </c>
+      <c r="K33">
+        <v>0.5</v>
+      </c>
+      <c r="L33">
+        <v>0.5</v>
+      </c>
+      <c r="M33">
+        <v>0.5</v>
+      </c>
+      <c r="N33">
+        <v>0</v>
+      </c>
+      <c r="O33">
+        <v>0.5</v>
+      </c>
+      <c r="P33">
+        <v>0.5</v>
+      </c>
+      <c r="Q33">
+        <v>1</v>
+      </c>
+      <c r="R33">
+        <v>0.5</v>
+      </c>
+      <c r="S33">
+        <v>1</v>
+      </c>
+      <c r="T33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20">
+      <c r="A34">
+        <v>640</v>
+      </c>
+      <c r="B34">
+        <v>0.24125</v>
+      </c>
+      <c r="C34">
+        <v>0.5</v>
+      </c>
+      <c r="D34">
+        <v>0.965</v>
+      </c>
+      <c r="E34">
+        <v>0.6109695669894349</v>
+      </c>
+      <c r="G34">
+        <v>1</v>
+      </c>
+      <c r="H34">
+        <v>0.97</v>
+      </c>
+      <c r="I34">
+        <v>1</v>
+      </c>
+      <c r="J34">
+        <v>1</v>
+      </c>
+      <c r="K34">
+        <v>0.5</v>
+      </c>
+      <c r="L34">
+        <v>0.5</v>
+      </c>
+      <c r="M34">
+        <v>0.5</v>
+      </c>
+      <c r="N34">
+        <v>0</v>
+      </c>
+      <c r="O34">
+        <v>0.5</v>
+      </c>
+      <c r="P34">
+        <v>0.5</v>
+      </c>
+      <c r="Q34">
+        <v>1</v>
+      </c>
+      <c r="R34">
+        <v>0.5</v>
+      </c>
+      <c r="S34">
+        <v>1</v>
+      </c>
+      <c r="T34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20">
+      <c r="A35">
+        <v>660</v>
+      </c>
+      <c r="B35">
+        <v>0.24125</v>
+      </c>
+      <c r="C35">
+        <v>0.5</v>
+      </c>
+      <c r="D35">
+        <v>0.965</v>
+      </c>
+      <c r="E35">
+        <v>0.6071260849330077</v>
+      </c>
+      <c r="G35">
+        <v>1</v>
+      </c>
+      <c r="H35">
+        <v>0.99</v>
+      </c>
+      <c r="I35">
+        <v>0.5</v>
+      </c>
+      <c r="J35">
+        <v>1</v>
+      </c>
+      <c r="K35">
+        <v>0.5</v>
+      </c>
+      <c r="L35">
+        <v>0.5</v>
+      </c>
+      <c r="M35">
+        <v>0.5</v>
+      </c>
+      <c r="N35">
+        <v>0</v>
+      </c>
+      <c r="O35">
+        <v>0.5</v>
+      </c>
+      <c r="P35">
+        <v>0.5</v>
+      </c>
+      <c r="Q35">
+        <v>1</v>
+      </c>
+      <c r="R35">
+        <v>0.5</v>
+      </c>
+      <c r="S35">
+        <v>1</v>
+      </c>
+      <c r="T35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20">
+      <c r="A36">
+        <v>680</v>
+      </c>
+      <c r="B36">
+        <v>0.24125</v>
+      </c>
+      <c r="C36">
+        <v>0.5</v>
+      </c>
+      <c r="D36">
+        <v>0.965</v>
+      </c>
+      <c r="E36">
+        <v>0.6071260849330077</v>
+      </c>
+      <c r="G36">
+        <v>1</v>
+      </c>
+      <c r="H36">
+        <v>0.99</v>
+      </c>
+      <c r="I36">
+        <v>0.5</v>
+      </c>
+      <c r="J36">
+        <v>1</v>
+      </c>
+      <c r="K36">
+        <v>0.5</v>
+      </c>
+      <c r="L36">
+        <v>0.5</v>
+      </c>
+      <c r="M36">
+        <v>0.5</v>
+      </c>
+      <c r="N36">
+        <v>0</v>
+      </c>
+      <c r="O36">
+        <v>0.5</v>
+      </c>
+      <c r="P36">
+        <v>0.5</v>
+      </c>
+      <c r="Q36">
+        <v>1</v>
+      </c>
+      <c r="R36">
+        <v>0.5</v>
+      </c>
+      <c r="S36">
+        <v>1</v>
+      </c>
+      <c r="T36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20">
+      <c r="A37">
+        <v>700</v>
+      </c>
+      <c r="B37">
+        <v>0.246099125</v>
+      </c>
+      <c r="C37">
+        <v>0.505</v>
+      </c>
+      <c r="D37">
+        <v>0.965</v>
+      </c>
+      <c r="E37">
+        <v>0.6071260849330077</v>
+      </c>
+      <c r="G37">
+        <v>1</v>
+      </c>
+      <c r="H37">
+        <v>0.99</v>
+      </c>
+      <c r="I37">
+        <v>0.5</v>
+      </c>
+      <c r="J37">
+        <v>1</v>
+      </c>
+      <c r="K37">
+        <v>0.5</v>
+      </c>
+      <c r="L37">
+        <v>0.5</v>
+      </c>
+      <c r="M37">
+        <v>0.5</v>
+      </c>
+      <c r="N37">
+        <v>0</v>
+      </c>
+      <c r="O37">
+        <v>0.5</v>
+      </c>
+      <c r="P37">
+        <v>0.5</v>
+      </c>
+      <c r="Q37">
+        <v>1</v>
+      </c>
+      <c r="R37">
+        <v>0.5</v>
+      </c>
+      <c r="S37">
+        <v>1</v>
+      </c>
+      <c r="T37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:20">
+      <c r="A38">
+        <v>720</v>
+      </c>
+      <c r="B38">
+        <v>0.246099125</v>
+      </c>
+      <c r="C38">
+        <v>0.505</v>
+      </c>
+      <c r="D38">
+        <v>0.965</v>
+      </c>
+      <c r="E38">
+        <v>0.6111108714768035</v>
+      </c>
+      <c r="G38">
+        <v>1</v>
+      </c>
+      <c r="H38">
+        <v>0.995</v>
+      </c>
+      <c r="I38">
+        <v>1</v>
+      </c>
+      <c r="J38">
+        <v>1</v>
+      </c>
+      <c r="K38">
+        <v>0.5</v>
+      </c>
+      <c r="L38">
+        <v>0.5</v>
+      </c>
+      <c r="M38">
+        <v>0.5</v>
+      </c>
+      <c r="N38">
+        <v>0</v>
+      </c>
+      <c r="O38">
+        <v>0.5</v>
+      </c>
+      <c r="P38">
+        <v>0.5</v>
+      </c>
+      <c r="Q38">
+        <v>1</v>
+      </c>
+      <c r="R38">
+        <v>0.5</v>
+      </c>
+      <c r="S38">
+        <v>1</v>
+      </c>
+      <c r="T38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:20">
+      <c r="A39">
+        <v>740</v>
+      </c>
+      <c r="B39">
+        <v>0.246099125</v>
+      </c>
+      <c r="C39">
+        <v>0.505</v>
+      </c>
+      <c r="D39">
+        <v>0.965</v>
+      </c>
+      <c r="E39">
+        <v>0.5763639032795477</v>
+      </c>
+      <c r="G39">
+        <v>1</v>
+      </c>
+      <c r="H39">
+        <v>1</v>
+      </c>
+      <c r="I39">
+        <v>1</v>
+      </c>
+      <c r="J39">
+        <v>1</v>
+      </c>
+      <c r="K39">
+        <v>0.5</v>
+      </c>
+      <c r="L39">
+        <v>0.5</v>
+      </c>
+      <c r="M39">
+        <v>0.5</v>
+      </c>
+      <c r="N39">
+        <v>0.5</v>
+      </c>
+      <c r="O39">
+        <v>0.5</v>
+      </c>
+      <c r="P39">
+        <v>1</v>
+      </c>
+      <c r="Q39">
+        <v>0.5</v>
+      </c>
+      <c r="R39">
+        <v>0.5</v>
+      </c>
+      <c r="S39">
+        <v>1</v>
+      </c>
+      <c r="T39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20">
+      <c r="A40">
+        <v>760</v>
+      </c>
+      <c r="B40">
+        <v>0.246099125</v>
+      </c>
+      <c r="C40">
+        <v>0.505</v>
+      </c>
+      <c r="D40">
+        <v>0.965</v>
+      </c>
+      <c r="E40">
+        <v>0.5723508558382779</v>
+      </c>
+      <c r="G40">
+        <v>1</v>
+      </c>
+      <c r="H40">
+        <v>0.99</v>
+      </c>
+      <c r="I40">
+        <v>0.5</v>
+      </c>
+      <c r="J40">
+        <v>1</v>
+      </c>
+      <c r="K40">
+        <v>0.5</v>
+      </c>
+      <c r="L40">
+        <v>0.5</v>
+      </c>
+      <c r="M40">
+        <v>0.5</v>
+      </c>
+      <c r="N40">
+        <v>0.5</v>
+      </c>
+      <c r="O40">
+        <v>0.5</v>
+      </c>
+      <c r="P40">
+        <v>1</v>
+      </c>
+      <c r="Q40">
+        <v>0.5</v>
+      </c>
+      <c r="R40">
+        <v>0.5</v>
+      </c>
+      <c r="S40">
+        <v>1</v>
+      </c>
+      <c r="T40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:20">
+      <c r="A41">
+        <v>780</v>
+      </c>
+      <c r="B41">
+        <v>0.246099125</v>
+      </c>
+      <c r="C41">
+        <v>0.505</v>
+      </c>
+      <c r="D41">
+        <v>0.965</v>
+      </c>
+      <c r="E41">
+        <v>0.5723508558382779</v>
+      </c>
+      <c r="G41">
+        <v>1</v>
+      </c>
+      <c r="H41">
+        <v>0.99</v>
+      </c>
+      <c r="I41">
+        <v>0.5</v>
+      </c>
+      <c r="J41">
+        <v>1</v>
+      </c>
+      <c r="K41">
+        <v>0.5</v>
+      </c>
+      <c r="L41">
+        <v>0.5</v>
+      </c>
+      <c r="M41">
+        <v>0.5</v>
+      </c>
+      <c r="N41">
+        <v>0.5</v>
+      </c>
+      <c r="O41">
+        <v>0.5</v>
+      </c>
+      <c r="P41">
+        <v>1</v>
+      </c>
+      <c r="Q41">
+        <v>0.5</v>
+      </c>
+      <c r="R41">
+        <v>0.5</v>
+      </c>
+      <c r="S41">
+        <v>1</v>
+      </c>
+      <c r="T41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:20">
+      <c r="A42">
+        <v>800</v>
+      </c>
+      <c r="B42">
+        <v>0.2509965</v>
+      </c>
+      <c r="C42">
+        <v>0.51</v>
+      </c>
+      <c r="D42">
+        <v>0.965</v>
+      </c>
+      <c r="E42">
+        <v>0.5762508596896527</v>
+      </c>
+      <c r="G42">
+        <v>1</v>
+      </c>
+      <c r="H42">
+        <v>0.98</v>
+      </c>
+      <c r="I42">
+        <v>1</v>
+      </c>
+      <c r="J42">
+        <v>1</v>
+      </c>
+      <c r="K42">
+        <v>0.5</v>
+      </c>
+      <c r="L42">
+        <v>0.5</v>
+      </c>
+      <c r="M42">
+        <v>0.5</v>
+      </c>
+      <c r="N42">
+        <v>0.5</v>
+      </c>
+      <c r="O42">
+        <v>0.5</v>
+      </c>
+      <c r="P42">
+        <v>1</v>
+      </c>
+      <c r="Q42">
+        <v>0.5</v>
+      </c>
+      <c r="R42">
+        <v>0.5</v>
+      </c>
+      <c r="S42">
+        <v>1</v>
+      </c>
+      <c r="T42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:20">
+      <c r="A43">
+        <v>820</v>
+      </c>
+      <c r="B43">
+        <v>0.2509965</v>
+      </c>
+      <c r="C43">
+        <v>0.51</v>
+      </c>
+      <c r="D43">
+        <v>0.965</v>
+      </c>
+      <c r="E43">
+        <v>0.5762791205871265</v>
+      </c>
+      <c r="G43">
+        <v>1</v>
+      </c>
+      <c r="H43">
+        <v>0.985</v>
+      </c>
+      <c r="I43">
+        <v>1</v>
+      </c>
+      <c r="J43">
+        <v>1</v>
+      </c>
+      <c r="K43">
+        <v>0.5</v>
+      </c>
+      <c r="L43">
+        <v>0.5</v>
+      </c>
+      <c r="M43">
+        <v>0.5</v>
+      </c>
+      <c r="N43">
+        <v>0.5</v>
+      </c>
+      <c r="O43">
+        <v>0.5</v>
+      </c>
+      <c r="P43">
+        <v>1</v>
+      </c>
+      <c r="Q43">
+        <v>0.5</v>
+      </c>
+      <c r="R43">
+        <v>0.5</v>
+      </c>
+      <c r="S43">
+        <v>1</v>
+      </c>
+      <c r="T43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:20">
+      <c r="A44">
+        <v>840</v>
+      </c>
+      <c r="B44">
+        <v>0.246099125</v>
+      </c>
+      <c r="C44">
+        <v>0.505</v>
+      </c>
+      <c r="D44">
+        <v>0.965</v>
+      </c>
+      <c r="E44">
+        <v>0.5723225949408043</v>
+      </c>
+      <c r="G44">
+        <v>1</v>
+      </c>
+      <c r="H44">
+        <v>0.985</v>
+      </c>
+      <c r="I44">
+        <v>0.5</v>
+      </c>
+      <c r="J44">
+        <v>1</v>
+      </c>
+      <c r="K44">
+        <v>0.5</v>
+      </c>
+      <c r="L44">
+        <v>0.5</v>
+      </c>
+      <c r="M44">
+        <v>0.5</v>
+      </c>
+      <c r="N44">
+        <v>0.5</v>
+      </c>
+      <c r="O44">
+        <v>0.5</v>
+      </c>
+      <c r="P44">
+        <v>1</v>
+      </c>
+      <c r="Q44">
+        <v>0.5</v>
+      </c>
+      <c r="R44">
+        <v>0.5</v>
+      </c>
+      <c r="S44">
+        <v>1</v>
+      </c>
+      <c r="T44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:20">
+      <c r="A45">
+        <v>860</v>
+      </c>
+      <c r="B45">
+        <v>0.246099125</v>
+      </c>
+      <c r="C45">
+        <v>0.505</v>
+      </c>
+      <c r="D45">
+        <v>0.965</v>
+      </c>
+      <c r="E45">
+        <v>0.5723508558382779</v>
+      </c>
+      <c r="G45">
+        <v>1</v>
+      </c>
+      <c r="H45">
+        <v>0.99</v>
+      </c>
+      <c r="I45">
+        <v>0.5</v>
+      </c>
+      <c r="J45">
+        <v>1</v>
+      </c>
+      <c r="K45">
+        <v>0.5</v>
+      </c>
+      <c r="L45">
+        <v>0.5</v>
+      </c>
+      <c r="M45">
+        <v>0.5</v>
+      </c>
+      <c r="N45">
+        <v>0.5</v>
+      </c>
+      <c r="O45">
+        <v>0.5</v>
+      </c>
+      <c r="P45">
+        <v>1</v>
+      </c>
+      <c r="Q45">
+        <v>0.5</v>
+      </c>
+      <c r="R45">
+        <v>0.5</v>
+      </c>
+      <c r="S45">
+        <v>1</v>
+      </c>
+      <c r="T45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:20">
+      <c r="A46">
+        <v>880</v>
+      </c>
+      <c r="B46">
+        <v>0.2509965</v>
+      </c>
+      <c r="C46">
+        <v>0.51</v>
+      </c>
+      <c r="D46">
+        <v>0.965</v>
+      </c>
+      <c r="E46">
+        <v>0.5723791167357518</v>
+      </c>
+      <c r="G46">
+        <v>1</v>
+      </c>
+      <c r="H46">
+        <v>0.995</v>
+      </c>
+      <c r="I46">
+        <v>0.5</v>
+      </c>
+      <c r="J46">
+        <v>1</v>
+      </c>
+      <c r="K46">
+        <v>0.5</v>
+      </c>
+      <c r="L46">
+        <v>0.5</v>
+      </c>
+      <c r="M46">
+        <v>0.5</v>
+      </c>
+      <c r="N46">
+        <v>0.5</v>
+      </c>
+      <c r="O46">
+        <v>0.5</v>
+      </c>
+      <c r="P46">
+        <v>1</v>
+      </c>
+      <c r="Q46">
+        <v>0.5</v>
+      </c>
+      <c r="R46">
+        <v>0.5</v>
+      </c>
+      <c r="S46">
+        <v>1</v>
+      </c>
+      <c r="T46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:20">
+      <c r="A47">
+        <v>900</v>
+      </c>
+      <c r="B47">
+        <v>0.2509965</v>
+      </c>
+      <c r="C47">
+        <v>0.51</v>
+      </c>
+      <c r="D47">
+        <v>0.965</v>
+      </c>
+      <c r="E47">
+        <v>0.5723508558382779</v>
+      </c>
+      <c r="G47">
+        <v>1</v>
+      </c>
+      <c r="H47">
+        <v>0.99</v>
+      </c>
+      <c r="I47">
+        <v>0.5</v>
+      </c>
+      <c r="J47">
+        <v>1</v>
+      </c>
+      <c r="K47">
+        <v>0.5</v>
+      </c>
+      <c r="L47">
+        <v>0.5</v>
+      </c>
+      <c r="M47">
+        <v>0.5</v>
+      </c>
+      <c r="N47">
+        <v>0.5</v>
+      </c>
+      <c r="O47">
+        <v>0.5</v>
+      </c>
+      <c r="P47">
+        <v>1</v>
+      </c>
+      <c r="Q47">
+        <v>0.5</v>
+      </c>
+      <c r="R47">
+        <v>0.5</v>
+      </c>
+      <c r="S47">
+        <v>1</v>
+      </c>
+      <c r="T47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:20">
+      <c r="A48">
+        <v>920</v>
+      </c>
+      <c r="B48">
+        <v>0.2509965</v>
+      </c>
+      <c r="C48">
+        <v>0.51</v>
+      </c>
+      <c r="D48">
+        <v>0.965</v>
+      </c>
+      <c r="E48">
+        <v>0.5724073776332255</v>
+      </c>
+      <c r="G48">
+        <v>1</v>
+      </c>
+      <c r="H48">
+        <v>1</v>
+      </c>
+      <c r="I48">
+        <v>0.5</v>
+      </c>
+      <c r="J48">
+        <v>1</v>
+      </c>
+      <c r="K48">
+        <v>0.5</v>
+      </c>
+      <c r="L48">
+        <v>0.5</v>
+      </c>
+      <c r="M48">
+        <v>0.5</v>
+      </c>
+      <c r="N48">
+        <v>0.5</v>
+      </c>
+      <c r="O48">
+        <v>0.5</v>
+      </c>
+      <c r="P48">
+        <v>1</v>
+      </c>
+      <c r="Q48">
+        <v>0.5</v>
+      </c>
+      <c r="R48">
+        <v>0.5</v>
+      </c>
+      <c r="S48">
+        <v>1</v>
+      </c>
+      <c r="T48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:20">
+      <c r="A49">
+        <v>940</v>
+      </c>
+      <c r="B49">
+        <v>0.0003031250000000001</v>
+      </c>
+      <c r="C49">
+        <v>0.025</v>
+      </c>
+      <c r="D49">
+        <v>0.485</v>
+      </c>
+      <c r="E49">
+        <v>0.5724073776332255</v>
+      </c>
+      <c r="G49">
+        <v>1</v>
+      </c>
+      <c r="H49">
+        <v>1</v>
+      </c>
+      <c r="I49">
+        <v>0.5</v>
+      </c>
+      <c r="J49">
+        <v>1</v>
+      </c>
+      <c r="K49">
+        <v>0.5</v>
+      </c>
+      <c r="L49">
+        <v>0.5</v>
+      </c>
+      <c r="M49">
+        <v>0.5</v>
+      </c>
+      <c r="N49">
+        <v>0.5</v>
+      </c>
+      <c r="O49">
+        <v>0.5</v>
+      </c>
+      <c r="P49">
+        <v>1</v>
+      </c>
+      <c r="Q49">
+        <v>0.5</v>
+      </c>
+      <c r="R49">
+        <v>0.5</v>
+      </c>
+      <c r="S49">
+        <v>1</v>
+      </c>
+      <c r="T49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:20">
+      <c r="A50">
+        <v>960</v>
+      </c>
+      <c r="B50">
+        <v>0.000195</v>
+      </c>
+      <c r="C50">
+        <v>0.02</v>
+      </c>
+      <c r="D50">
+        <v>0.4875</v>
+      </c>
+      <c r="E50">
+        <v>0.5139326224545487</v>
+      </c>
+      <c r="G50">
+        <v>1</v>
+      </c>
+      <c r="H50">
+        <v>0.985</v>
+      </c>
+      <c r="I50">
+        <v>0.5</v>
+      </c>
+      <c r="J50">
+        <v>1</v>
+      </c>
+      <c r="K50">
+        <v>0.5</v>
+      </c>
+      <c r="L50">
+        <v>0.5</v>
+      </c>
+      <c r="M50">
+        <v>0.5</v>
+      </c>
+      <c r="N50">
+        <v>0.5</v>
+      </c>
+      <c r="O50">
+        <v>0.5</v>
+      </c>
+      <c r="P50">
+        <v>0.5</v>
+      </c>
+      <c r="Q50">
+        <v>0.5</v>
+      </c>
+      <c r="R50">
+        <v>0.5</v>
+      </c>
+      <c r="S50">
+        <v>1</v>
+      </c>
+      <c r="T50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:20">
+      <c r="A51">
+        <v>980</v>
+      </c>
+      <c r="B51">
+        <v>0.000195</v>
+      </c>
+      <c r="C51">
+        <v>0.02</v>
+      </c>
+      <c r="D51">
+        <v>0.4875</v>
+      </c>
+      <c r="E51">
+        <v>0.5248458506230042</v>
+      </c>
+      <c r="G51">
+        <v>1</v>
+      </c>
+      <c r="H51">
+        <v>0.995</v>
+      </c>
+      <c r="I51">
+        <v>0.5</v>
+      </c>
+      <c r="J51">
+        <v>1</v>
+      </c>
+      <c r="K51">
+        <v>0.5</v>
+      </c>
+      <c r="L51">
+        <v>1</v>
+      </c>
+      <c r="M51">
+        <v>0.5</v>
+      </c>
+      <c r="N51">
+        <v>0.5</v>
+      </c>
+      <c r="O51">
+        <v>0.5</v>
+      </c>
+      <c r="P51">
+        <v>0.5</v>
+      </c>
+      <c r="Q51">
+        <v>0.5</v>
+      </c>
+      <c r="R51">
+        <v>0.5</v>
+      </c>
+      <c r="S51">
+        <v>1</v>
+      </c>
+      <c r="T51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:20">
+      <c r="A52">
+        <v>1000</v>
+      </c>
+      <c r="B52">
+        <v>0.000195</v>
+      </c>
+      <c r="C52">
+        <v>0.02</v>
+      </c>
+      <c r="D52">
+        <v>0.4875</v>
+      </c>
+      <c r="E52">
+        <v>0.5247045461356356</v>
+      </c>
+      <c r="G52">
+        <v>1</v>
+      </c>
+      <c r="H52">
+        <v>0.97</v>
+      </c>
+      <c r="I52">
+        <v>0.5</v>
+      </c>
+      <c r="J52">
+        <v>1</v>
+      </c>
+      <c r="K52">
+        <v>0.5</v>
+      </c>
+      <c r="L52">
+        <v>1</v>
+      </c>
+      <c r="M52">
+        <v>0.5</v>
+      </c>
+      <c r="N52">
+        <v>0.5</v>
+      </c>
+      <c r="O52">
+        <v>0.5</v>
+      </c>
+      <c r="P52">
+        <v>0.5</v>
+      </c>
+      <c r="Q52">
+        <v>0.5</v>
+      </c>
+      <c r="R52">
+        <v>0.5</v>
+      </c>
+      <c r="S52">
+        <v>1</v>
+      </c>
+      <c r="T52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:20">
+      <c r="A53">
+        <v>1020</v>
+      </c>
+      <c r="B53">
+        <v>0.000387</v>
+      </c>
+      <c r="C53">
+        <v>0.02</v>
+      </c>
+      <c r="D53">
+        <v>0.9675</v>
+      </c>
+      <c r="E53">
+        <v>0.5247893288280567</v>
+      </c>
+      <c r="G53">
+        <v>1</v>
+      </c>
+      <c r="H53">
+        <v>0.985</v>
+      </c>
+      <c r="I53">
+        <v>0.5</v>
+      </c>
+      <c r="J53">
+        <v>1</v>
+      </c>
+      <c r="K53">
+        <v>0.5</v>
+      </c>
+      <c r="L53">
+        <v>1</v>
+      </c>
+      <c r="M53">
+        <v>0.5</v>
+      </c>
+      <c r="N53">
+        <v>0.5</v>
+      </c>
+      <c r="O53">
+        <v>0.5</v>
+      </c>
+      <c r="P53">
+        <v>0.5</v>
+      </c>
+      <c r="Q53">
+        <v>0.5</v>
+      </c>
+      <c r="R53">
+        <v>0.5</v>
+      </c>
+      <c r="S53">
+        <v>1</v>
+      </c>
+      <c r="T53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:20">
+      <c r="A54">
+        <v>1040</v>
+      </c>
+      <c r="B54">
+        <v>0.121875</v>
+      </c>
+      <c r="C54">
+        <v>0.5</v>
+      </c>
+      <c r="D54">
+        <v>0.4875</v>
+      </c>
+      <c r="E54">
+        <v>0.5248175897255304</v>
+      </c>
+      <c r="G54">
+        <v>1</v>
+      </c>
+      <c r="H54">
+        <v>0.99</v>
+      </c>
+      <c r="I54">
+        <v>0.5</v>
+      </c>
+      <c r="J54">
+        <v>1</v>
+      </c>
+      <c r="K54">
+        <v>0.5</v>
+      </c>
+      <c r="L54">
+        <v>1</v>
+      </c>
+      <c r="M54">
+        <v>0.5</v>
+      </c>
+      <c r="N54">
+        <v>0.5</v>
+      </c>
+      <c r="O54">
+        <v>0.5</v>
+      </c>
+      <c r="P54">
+        <v>0.5</v>
+      </c>
+      <c r="Q54">
+        <v>0.5</v>
+      </c>
+      <c r="R54">
+        <v>0.5</v>
+      </c>
+      <c r="S54">
+        <v>1</v>
+      </c>
+      <c r="T54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:20">
+      <c r="A55">
+        <v>1060</v>
+      </c>
+      <c r="B55">
+        <v>0.12006225</v>
+      </c>
+      <c r="C55">
+        <v>0.495</v>
+      </c>
+      <c r="D55">
+        <v>0.49</v>
+      </c>
+      <c r="E55">
+        <v>0.5139608833520225</v>
+      </c>
+      <c r="G55">
+        <v>1</v>
+      </c>
+      <c r="H55">
+        <v>0.99</v>
+      </c>
+      <c r="I55">
+        <v>0.5</v>
+      </c>
+      <c r="J55">
+        <v>1</v>
+      </c>
+      <c r="K55">
+        <v>0.5</v>
+      </c>
+      <c r="L55">
+        <v>0.5</v>
+      </c>
+      <c r="M55">
+        <v>0.5</v>
+      </c>
+      <c r="N55">
+        <v>0.5</v>
+      </c>
+      <c r="O55">
+        <v>0.5</v>
+      </c>
+      <c r="P55">
+        <v>0.5</v>
+      </c>
+      <c r="Q55">
+        <v>0.5</v>
+      </c>
+      <c r="R55">
+        <v>0.5</v>
+      </c>
+      <c r="S55">
+        <v>1</v>
+      </c>
+      <c r="T55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:20">
+      <c r="A56">
+        <v>1080</v>
+      </c>
+      <c r="B56">
+        <v>0.1225</v>
+      </c>
+      <c r="C56">
+        <v>0.5</v>
+      </c>
+      <c r="D56">
+        <v>0.49</v>
+      </c>
+      <c r="E56">
+        <v>0.5248175897255304</v>
+      </c>
+      <c r="G56">
+        <v>1</v>
+      </c>
+      <c r="H56">
+        <v>0.99</v>
+      </c>
+      <c r="I56">
+        <v>0.5</v>
+      </c>
+      <c r="J56">
+        <v>1</v>
+      </c>
+      <c r="K56">
+        <v>0.5</v>
+      </c>
+      <c r="L56">
+        <v>1</v>
+      </c>
+      <c r="M56">
+        <v>0.5</v>
+      </c>
+      <c r="N56">
+        <v>0.5</v>
+      </c>
+      <c r="O56">
+        <v>0.5</v>
+      </c>
+      <c r="P56">
+        <v>0.5</v>
+      </c>
+      <c r="Q56">
+        <v>0.5</v>
+      </c>
+      <c r="R56">
+        <v>0.5</v>
+      </c>
+      <c r="S56">
+        <v>1</v>
+      </c>
+      <c r="T56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:20">
+      <c r="A57">
+        <v>1100</v>
+      </c>
+      <c r="B57">
+        <v>0.26471025</v>
+      </c>
+      <c r="C57">
+        <v>0.735</v>
+      </c>
+      <c r="D57">
+        <v>0.49</v>
+      </c>
+      <c r="E57">
+        <v>0.4452049945421466</v>
+      </c>
+      <c r="G57">
+        <v>1</v>
+      </c>
+      <c r="H57">
+        <v>1</v>
+      </c>
+      <c r="I57">
+        <v>0.5</v>
+      </c>
+      <c r="J57">
+        <v>1</v>
+      </c>
+      <c r="K57">
+        <v>0.5</v>
+      </c>
+      <c r="L57">
+        <v>1</v>
+      </c>
+      <c r="M57">
+        <v>0.5</v>
+      </c>
+      <c r="N57">
+        <v>0</v>
+      </c>
+      <c r="O57">
+        <v>0.5</v>
+      </c>
+      <c r="P57">
+        <v>0</v>
+      </c>
+      <c r="Q57">
+        <v>0.5</v>
+      </c>
+      <c r="R57">
+        <v>0.5</v>
+      </c>
+      <c r="S57">
+        <v>1</v>
+      </c>
+      <c r="T57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:20">
+      <c r="A58">
+        <v>1120</v>
+      </c>
+      <c r="B58">
+        <v>0.26471025</v>
+      </c>
+      <c r="C58">
+        <v>0.735</v>
+      </c>
+      <c r="D58">
+        <v>0.49</v>
+      </c>
+      <c r="E58">
+        <v>0.4451202118497255</v>
+      </c>
+      <c r="G58">
+        <v>1</v>
+      </c>
+      <c r="H58">
+        <v>0.985</v>
+      </c>
+      <c r="I58">
+        <v>0.5</v>
+      </c>
+      <c r="J58">
+        <v>1</v>
+      </c>
+      <c r="K58">
+        <v>0.5</v>
+      </c>
+      <c r="L58">
+        <v>1</v>
+      </c>
+      <c r="M58">
+        <v>0.5</v>
+      </c>
+      <c r="N58">
+        <v>0</v>
+      </c>
+      <c r="O58">
+        <v>0.5</v>
+      </c>
+      <c r="P58">
+        <v>0</v>
+      </c>
+      <c r="Q58">
+        <v>0.5</v>
+      </c>
+      <c r="R58">
+        <v>0.5</v>
+      </c>
+      <c r="S58">
+        <v>1</v>
+      </c>
+      <c r="T58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:20">
+      <c r="A59">
+        <v>1140</v>
+      </c>
+      <c r="B59">
+        <v>0.266955</v>
+      </c>
+      <c r="C59">
+        <v>0.74</v>
+      </c>
+      <c r="D59">
+        <v>0.4875</v>
+      </c>
+      <c r="E59">
+        <v>0.5139608833520225</v>
+      </c>
+      <c r="G59">
+        <v>1</v>
+      </c>
+      <c r="H59">
+        <v>0.99</v>
+      </c>
+      <c r="I59">
+        <v>0.5</v>
+      </c>
+      <c r="J59">
+        <v>1</v>
+      </c>
+      <c r="K59">
+        <v>0.5</v>
+      </c>
+      <c r="L59">
+        <v>0.5</v>
+      </c>
+      <c r="M59">
+        <v>0.5</v>
+      </c>
+      <c r="N59">
+        <v>0.5</v>
+      </c>
+      <c r="O59">
+        <v>0.5</v>
+      </c>
+      <c r="P59">
+        <v>0.5</v>
+      </c>
+      <c r="Q59">
+        <v>0.5</v>
+      </c>
+      <c r="R59">
+        <v>0.5</v>
+      </c>
+      <c r="S59">
+        <v>1</v>
+      </c>
+      <c r="T59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:20">
+      <c r="A60">
+        <v>1160</v>
+      </c>
+      <c r="B60">
+        <v>0.265586</v>
+      </c>
+      <c r="C60">
+        <v>0.74</v>
+      </c>
+      <c r="D60">
+        <v>0.485</v>
+      </c>
+      <c r="E60">
+        <v>0.4926534779624731</v>
+      </c>
+      <c r="G60">
+        <v>1</v>
+      </c>
+      <c r="H60">
+        <v>0.985</v>
+      </c>
+      <c r="I60">
+        <v>0.5</v>
+      </c>
+      <c r="J60">
+        <v>1</v>
+      </c>
+      <c r="K60">
+        <v>0.5</v>
+      </c>
+      <c r="L60">
+        <v>0.5</v>
+      </c>
+      <c r="M60">
+        <v>0.5</v>
+      </c>
+      <c r="N60">
+        <v>0</v>
+      </c>
+      <c r="O60">
+        <v>0.5</v>
+      </c>
+      <c r="P60">
+        <v>0.5</v>
+      </c>
+      <c r="Q60">
+        <v>0.5</v>
+      </c>
+      <c r="R60">
+        <v>0.5</v>
+      </c>
+      <c r="S60">
+        <v>1</v>
+      </c>
+      <c r="T60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:20">
+      <c r="A61">
+        <v>1180</v>
+      </c>
+      <c r="B61">
+        <v>0.032786</v>
+      </c>
+      <c r="C61">
+        <v>0.26</v>
+      </c>
+      <c r="D61">
+        <v>0.485</v>
+      </c>
+      <c r="E61">
+        <v>0.4926534779624731</v>
+      </c>
+      <c r="G61">
+        <v>1</v>
+      </c>
+      <c r="H61">
+        <v>0.985</v>
+      </c>
+      <c r="I61">
+        <v>0.5</v>
+      </c>
+      <c r="J61">
+        <v>1</v>
+      </c>
+      <c r="K61">
+        <v>0.5</v>
+      </c>
+      <c r="L61">
+        <v>0.5</v>
+      </c>
+      <c r="M61">
+        <v>0.5</v>
+      </c>
+      <c r="N61">
+        <v>0</v>
+      </c>
+      <c r="O61">
+        <v>0.5</v>
+      </c>
+      <c r="P61">
+        <v>0.5</v>
+      </c>
+      <c r="Q61">
+        <v>0.5</v>
+      </c>
+      <c r="R61">
+        <v>0.5</v>
+      </c>
+      <c r="S61">
+        <v>1</v>
+      </c>
+      <c r="T61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:20">
+      <c r="A62">
+        <v>1200</v>
+      </c>
+      <c r="B62">
+        <v>0.032786</v>
+      </c>
+      <c r="C62">
+        <v>0.26</v>
+      </c>
+      <c r="D62">
+        <v>0.485</v>
+      </c>
+      <c r="E62">
+        <v>0.4342635054762174</v>
+      </c>
+      <c r="G62">
+        <v>1</v>
+      </c>
+      <c r="H62">
+        <v>0.985</v>
+      </c>
+      <c r="I62">
+        <v>0.5</v>
+      </c>
+      <c r="J62">
+        <v>1</v>
+      </c>
+      <c r="K62">
+        <v>0.5</v>
+      </c>
+      <c r="L62">
+        <v>0.5</v>
+      </c>
+      <c r="M62">
+        <v>0.5</v>
+      </c>
+      <c r="N62">
+        <v>0</v>
+      </c>
+      <c r="O62">
+        <v>0.5</v>
+      </c>
+      <c r="P62">
+        <v>0</v>
+      </c>
+      <c r="Q62">
+        <v>0.5</v>
+      </c>
+      <c r="R62">
+        <v>0.5</v>
+      </c>
+      <c r="S62">
+        <v>1</v>
+      </c>
+      <c r="T62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:20">
+      <c r="A63">
+        <v>1220</v>
+      </c>
+      <c r="B63">
+        <v>0.265586</v>
+      </c>
+      <c r="C63">
+        <v>0.74</v>
+      </c>
+      <c r="D63">
+        <v>0.485</v>
+      </c>
+      <c r="E63">
+        <v>0.4343200272711649</v>
+      </c>
+      <c r="G63">
+        <v>1</v>
+      </c>
+      <c r="H63">
+        <v>0.995</v>
+      </c>
+      <c r="I63">
+        <v>0.5</v>
+      </c>
+      <c r="J63">
+        <v>1</v>
+      </c>
+      <c r="K63">
+        <v>0.5</v>
+      </c>
+      <c r="L63">
+        <v>0.5</v>
+      </c>
+      <c r="M63">
+        <v>0.5</v>
+      </c>
+      <c r="N63">
+        <v>0</v>
+      </c>
+      <c r="O63">
+        <v>0.5</v>
+      </c>
+      <c r="P63">
+        <v>0</v>
+      </c>
+      <c r="Q63">
+        <v>0.5</v>
+      </c>
+      <c r="R63">
+        <v>0.5</v>
+      </c>
+      <c r="S63">
+        <v>1</v>
+      </c>
+      <c r="T63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:20">
+      <c r="A64">
+        <v>1240</v>
+      </c>
+      <c r="B64">
+        <v>0.535599125</v>
+      </c>
+      <c r="C64">
+        <v>0.745</v>
+      </c>
+      <c r="D64">
+        <v>0.965</v>
+      </c>
+      <c r="E64">
+        <v>0.4044727031873116</v>
+      </c>
+      <c r="G64">
+        <v>1</v>
+      </c>
+      <c r="H64">
+        <v>0.985</v>
+      </c>
+      <c r="I64">
+        <v>0.5</v>
+      </c>
+      <c r="J64">
+        <v>1</v>
+      </c>
+      <c r="K64">
+        <v>0.5</v>
+      </c>
+      <c r="L64">
+        <v>0.5</v>
+      </c>
+      <c r="M64">
+        <v>0.5</v>
+      </c>
+      <c r="N64">
+        <v>0</v>
+      </c>
+      <c r="O64">
+        <v>0</v>
+      </c>
+      <c r="P64">
+        <v>0</v>
+      </c>
+      <c r="Q64">
+        <v>0.5</v>
+      </c>
+      <c r="R64">
+        <v>0.5</v>
+      </c>
+      <c r="S64">
+        <v>1</v>
+      </c>
+      <c r="T64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:20">
+      <c r="A65">
+        <v>1260</v>
+      </c>
+      <c r="B65">
+        <v>0.535599125</v>
+      </c>
+      <c r="C65">
+        <v>0.745</v>
+      </c>
+      <c r="D65">
+        <v>0.965</v>
+      </c>
+      <c r="E65">
+        <v>0.4045292249822591</v>
+      </c>
+      <c r="G65">
+        <v>1</v>
+      </c>
+      <c r="H65">
+        <v>0.995</v>
+      </c>
+      <c r="I65">
+        <v>0.5</v>
+      </c>
+      <c r="J65">
+        <v>1</v>
+      </c>
+      <c r="K65">
+        <v>0.5</v>
+      </c>
+      <c r="L65">
+        <v>0.5</v>
+      </c>
+      <c r="M65">
+        <v>0.5</v>
+      </c>
+      <c r="N65">
+        <v>0</v>
+      </c>
+      <c r="O65">
+        <v>0</v>
+      </c>
+      <c r="P65">
+        <v>0</v>
+      </c>
+      <c r="Q65">
+        <v>0.5</v>
+      </c>
+      <c r="R65">
+        <v>0.5</v>
+      </c>
+      <c r="S65">
+        <v>1</v>
+      </c>
+      <c r="T65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:20">
+      <c r="A66">
+        <v>1280</v>
+      </c>
+      <c r="B66">
+        <v>0.2454615625</v>
+      </c>
+      <c r="C66">
+        <v>0.505</v>
+      </c>
+      <c r="D66">
+        <v>0.9625</v>
+      </c>
+      <c r="E66">
+        <v>0.4045574858797328</v>
+      </c>
+      <c r="G66">
+        <v>1</v>
+      </c>
+      <c r="H66">
+        <v>1</v>
+      </c>
+      <c r="I66">
+        <v>0.5</v>
+      </c>
+      <c r="J66">
+        <v>1</v>
+      </c>
+      <c r="K66">
+        <v>0.5</v>
+      </c>
+      <c r="L66">
+        <v>0.5</v>
+      </c>
+      <c r="M66">
+        <v>0.5</v>
+      </c>
+      <c r="N66">
+        <v>0</v>
+      </c>
+      <c r="O66">
+        <v>0</v>
+      </c>
+      <c r="P66">
+        <v>0</v>
+      </c>
+      <c r="Q66">
+        <v>0.5</v>
+      </c>
+      <c r="R66">
+        <v>0.5</v>
+      </c>
+      <c r="S66">
+        <v>1</v>
+      </c>
+      <c r="T66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:20">
+      <c r="A67">
+        <v>1300</v>
+      </c>
+      <c r="B67">
+        <v>0.23884353125</v>
+      </c>
+      <c r="C67">
+        <v>0.4975</v>
+      </c>
+      <c r="D67">
+        <v>0.965</v>
+      </c>
+      <c r="E67">
+        <v>0.3936159968138036</v>
+      </c>
+      <c r="G67">
+        <v>1</v>
+      </c>
+      <c r="H67">
+        <v>0.985</v>
+      </c>
+      <c r="I67">
+        <v>0.5</v>
+      </c>
+      <c r="J67">
+        <v>1</v>
+      </c>
+      <c r="K67">
+        <v>0.5</v>
+      </c>
+      <c r="L67">
+        <v>0</v>
+      </c>
+      <c r="M67">
+        <v>0.5</v>
+      </c>
+      <c r="N67">
+        <v>0</v>
+      </c>
+      <c r="O67">
+        <v>0</v>
+      </c>
+      <c r="P67">
+        <v>0</v>
+      </c>
+      <c r="Q67">
+        <v>0.5</v>
+      </c>
+      <c r="R67">
+        <v>0.5</v>
+      </c>
+      <c r="S67">
+        <v>1</v>
+      </c>
+      <c r="T67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:20">
+      <c r="A68">
+        <v>1320</v>
+      </c>
+      <c r="B68">
+        <v>0.236449125</v>
+      </c>
+      <c r="C68">
+        <v>0.495</v>
+      </c>
+      <c r="D68">
+        <v>0.965</v>
+      </c>
+      <c r="E68">
+        <v>0.4520624910950067</v>
+      </c>
+      <c r="G68">
+        <v>1</v>
+      </c>
+      <c r="H68">
+        <v>0.995</v>
+      </c>
+      <c r="I68">
+        <v>0.5</v>
+      </c>
+      <c r="J68">
+        <v>1</v>
+      </c>
+      <c r="K68">
+        <v>0.5</v>
+      </c>
+      <c r="L68">
+        <v>0</v>
+      </c>
+      <c r="M68">
+        <v>0.5</v>
+      </c>
+      <c r="N68">
+        <v>0</v>
+      </c>
+      <c r="O68">
+        <v>0</v>
+      </c>
+      <c r="P68">
+        <v>0.5</v>
+      </c>
+      <c r="Q68">
+        <v>0.5</v>
+      </c>
+      <c r="R68">
+        <v>0.5</v>
+      </c>
+      <c r="S68">
+        <v>1</v>
+      </c>
+      <c r="T68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:20">
+      <c r="A69">
+        <v>1340</v>
+      </c>
+      <c r="B69">
+        <v>0.24125</v>
+      </c>
+      <c r="C69">
+        <v>0.5</v>
+      </c>
+      <c r="D69">
+        <v>0.965</v>
+      </c>
+      <c r="E69">
+        <v>0.4520624910950067</v>
+      </c>
+      <c r="G69">
+        <v>1</v>
+      </c>
+      <c r="H69">
+        <v>0.995</v>
+      </c>
+      <c r="I69">
+        <v>0.5</v>
+      </c>
+      <c r="J69">
+        <v>1</v>
+      </c>
+      <c r="K69">
+        <v>0.5</v>
+      </c>
+      <c r="L69">
+        <v>0</v>
+      </c>
+      <c r="M69">
+        <v>0.5</v>
+      </c>
+      <c r="N69">
+        <v>0</v>
+      </c>
+      <c r="O69">
+        <v>0</v>
+      </c>
+      <c r="P69">
+        <v>0.5</v>
+      </c>
+      <c r="Q69">
+        <v>0.5</v>
+      </c>
+      <c r="R69">
+        <v>0.5</v>
+      </c>
+      <c r="S69">
+        <v>1</v>
+      </c>
+      <c r="T69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:20">
+      <c r="A70">
+        <v>1360</v>
+      </c>
+      <c r="B70">
+        <v>0.24125</v>
+      </c>
+      <c r="C70">
+        <v>0.5</v>
+      </c>
+      <c r="D70">
+        <v>0.965</v>
+      </c>
+      <c r="E70">
+        <v>0.4629474583659883</v>
+      </c>
+      <c r="G70">
+        <v>1</v>
+      </c>
+      <c r="H70">
+        <v>1</v>
+      </c>
+      <c r="I70">
+        <v>0.5</v>
+      </c>
+      <c r="J70">
+        <v>1</v>
+      </c>
+      <c r="K70">
+        <v>0.5</v>
+      </c>
+      <c r="L70">
+        <v>0.5</v>
+      </c>
+      <c r="M70">
+        <v>0.5</v>
+      </c>
+      <c r="N70">
+        <v>0</v>
+      </c>
+      <c r="O70">
+        <v>0</v>
+      </c>
+      <c r="P70">
+        <v>0.5</v>
+      </c>
+      <c r="Q70">
+        <v>0.5</v>
+      </c>
+      <c r="R70">
+        <v>0.5</v>
+      </c>
+      <c r="S70">
+        <v>1</v>
+      </c>
+      <c r="T70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:20">
+      <c r="A71">
+        <v>1380</v>
+      </c>
+      <c r="B71">
+        <v>0.246099125</v>
+      </c>
+      <c r="C71">
+        <v>0.505</v>
+      </c>
+      <c r="D71">
+        <v>0.965</v>
+      </c>
+      <c r="E71">
+        <v>0.4629191974685146</v>
+      </c>
+      <c r="G71">
+        <v>1</v>
+      </c>
+      <c r="H71">
+        <v>0.995</v>
+      </c>
+      <c r="I71">
+        <v>0.5</v>
+      </c>
+      <c r="J71">
+        <v>1</v>
+      </c>
+      <c r="K71">
+        <v>0.5</v>
+      </c>
+      <c r="L71">
+        <v>0.5</v>
+      </c>
+      <c r="M71">
+        <v>0.5</v>
+      </c>
+      <c r="N71">
+        <v>0</v>
+      </c>
+      <c r="O71">
+        <v>0</v>
+      </c>
+      <c r="P71">
+        <v>0.5</v>
+      </c>
+      <c r="Q71">
+        <v>0.5</v>
+      </c>
+      <c r="R71">
+        <v>0.5</v>
+      </c>
+      <c r="S71">
+        <v>1</v>
+      </c>
+      <c r="T71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:20">
+      <c r="A72">
+        <v>1400</v>
+      </c>
+      <c r="B72">
+        <v>0.12125</v>
+      </c>
+      <c r="C72">
+        <v>0.5</v>
+      </c>
+      <c r="D72">
+        <v>0.485</v>
+      </c>
+      <c r="E72">
+        <v>0.4628909365710409</v>
+      </c>
+      <c r="G72">
+        <v>1</v>
+      </c>
+      <c r="H72">
+        <v>0.99</v>
+      </c>
+      <c r="I72">
+        <v>0.5</v>
+      </c>
+      <c r="J72">
+        <v>1</v>
+      </c>
+      <c r="K72">
+        <v>0.5</v>
+      </c>
+      <c r="L72">
+        <v>0.5</v>
+      </c>
+      <c r="M72">
+        <v>0.5</v>
+      </c>
+      <c r="N72">
+        <v>0</v>
+      </c>
+      <c r="O72">
+        <v>0</v>
+      </c>
+      <c r="P72">
+        <v>0.5</v>
+      </c>
+      <c r="Q72">
+        <v>0.5</v>
+      </c>
+      <c r="R72">
+        <v>0.5</v>
+      </c>
+      <c r="S72">
+        <v>1</v>
+      </c>
+      <c r="T72">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
